--- a/web/public/forms/orig/o-cheukryang-bogoseo.xlsx
+++ b/web/public/forms/orig/o-cheukryang-bogoseo.xlsx
@@ -2429,7 +2429,7 @@
     <row r="105" ht="10.5" customHeight="1">
       <c r="K105" s="37" t="inlineStr">
         <is>
-          <t>1) 과업위치 : 강원도 ○○○ 수상리  일원</t>
+          <t xml:space="preserve">1) 과업위치 : ○○도 ○○군 ○○리  일원</t>
         </is>
       </c>
     </row>

--- a/web/public/forms/orig/o-cheukryang-bogoseo.xlsx
+++ b/web/public/forms/orig/o-cheukryang-bogoseo.xlsx
@@ -758,7 +758,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
         </is>
       </c>
       <c r="G1" s="2" t="inlineStr">
@@ -848,7 +848,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
         </is>
       </c>
       <c r="G1" s="2" t="inlineStr">
@@ -1881,7 +1881,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
         </is>
       </c>
       <c r="G1" s="2" t="inlineStr">
@@ -2669,7 +2669,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
         </is>
       </c>
       <c r="G1" s="2" t="inlineStr">
@@ -4296,7 +4296,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
         </is>
       </c>
       <c r="G1" s="50" t="inlineStr">
@@ -4385,7 +4385,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
         </is>
       </c>
       <c r="G1" s="50" t="inlineStr">
@@ -5517,7 +5517,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
         </is>
       </c>
       <c r="G1" s="50" t="inlineStr">
@@ -6362,7 +6362,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
         </is>
       </c>
       <c r="G1" s="50" t="inlineStr">

--- a/web/public/forms/orig/o-cheukryang-bogoseo.xlsx
+++ b/web/public/forms/orig/o-cheukryang-bogoseo.xlsx
@@ -747,7 +747,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
         </is>
       </c>
       <c r="G1" s="2" t="inlineStr">
@@ -838,7 +838,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
         </is>
       </c>
       <c r="G1" s="2" t="inlineStr">
@@ -1851,7 +1851,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
         </is>
       </c>
       <c r="G1" s="2" t="inlineStr">
@@ -2628,7 +2628,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
         </is>
       </c>
       <c r="G1" s="2" t="inlineStr">
